--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J432"/>
+  <dimension ref="A1:J433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15996,6 +15996,42 @@
       <c r="J432" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>334.76</v>
+      </c>
+      <c r="C433" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="D433" t="n">
+        <v>333.85</v>
+      </c>
+      <c r="E433" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="F433" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="G433" t="n">
+        <v>334.79</v>
+      </c>
+      <c r="H433" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="I433" t="n">
+        <v>355.46</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B455"/>
+  <dimension ref="A1:B456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20563,6 +20599,16 @@
       </c>
       <c r="B455" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -20731,28 +20777,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2890297260801569</v>
+        <v>-0.2879963137030837</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K2" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1140129038975042</v>
+        <v>0.1137215599505161</v>
       </c>
       <c r="M2" t="n">
-        <v>4.859912428796082</v>
+        <v>4.854100624795321</v>
       </c>
       <c r="N2" t="n">
-        <v>38.02004216484677</v>
+        <v>37.94553524542334</v>
       </c>
       <c r="O2" t="n">
-        <v>6.166039422907282</v>
+        <v>6.159994743944457</v>
       </c>
       <c r="P2" t="n">
-        <v>339.956418389177</v>
+        <v>339.9459510659395</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20809,28 +20855,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3549985199482297</v>
+        <v>-0.3533941220194364</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K3" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1869247403547147</v>
+        <v>0.1860989421348885</v>
       </c>
       <c r="M3" t="n">
-        <v>4.599588870987015</v>
+        <v>4.597703609232862</v>
       </c>
       <c r="N3" t="n">
-        <v>32.10489304157709</v>
+        <v>32.06312151666916</v>
       </c>
       <c r="O3" t="n">
-        <v>5.666117986909299</v>
+        <v>5.662430707449687</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5299938641435</v>
+        <v>338.5137430894337</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20887,28 +20933,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2373560435319629</v>
+        <v>-0.2355659293885243</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1552805863476685</v>
+        <v>0.1536131024601752</v>
       </c>
       <c r="M4" t="n">
-        <v>3.390990444002696</v>
+        <v>3.394361421005534</v>
       </c>
       <c r="N4" t="n">
-        <v>17.94940610402984</v>
+        <v>17.94837252875347</v>
       </c>
       <c r="O4" t="n">
-        <v>4.236673943558772</v>
+        <v>4.236551962239278</v>
       </c>
       <c r="P4" t="n">
-        <v>335.9111014118263</v>
+        <v>335.8929695374778</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20965,28 +21011,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04366460409541903</v>
+        <v>-0.0428995061898271</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01089695643748212</v>
+        <v>0.01056309801776889</v>
       </c>
       <c r="M5" t="n">
-        <v>2.505208603252627</v>
+        <v>2.503521247291516</v>
       </c>
       <c r="N5" t="n">
-        <v>10.13560224915004</v>
+        <v>10.11954135139022</v>
       </c>
       <c r="O5" t="n">
-        <v>3.183646062166779</v>
+        <v>3.181122655822975</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1921561712174</v>
+        <v>335.1844065765118</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21043,28 +21089,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02508469800815288</v>
+        <v>0.02518460489268516</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K6" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00291238272312766</v>
+        <v>0.002949119454203508</v>
       </c>
       <c r="M6" t="n">
-        <v>2.902147553647732</v>
+        <v>2.89602259901261</v>
       </c>
       <c r="N6" t="n">
-        <v>12.61702062097613</v>
+        <v>12.58794075365855</v>
       </c>
       <c r="O6" t="n">
-        <v>3.552044569114544</v>
+        <v>3.547948809334564</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3041884330894</v>
+        <v>337.303176486961</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21121,28 +21167,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09460413612050565</v>
+        <v>-0.09583467928313913</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K7" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02616849323966686</v>
+        <v>0.0269307530603401</v>
       </c>
       <c r="M7" t="n">
-        <v>3.704973802721539</v>
+        <v>3.702686907248831</v>
       </c>
       <c r="N7" t="n">
-        <v>19.50650821825044</v>
+        <v>19.48049940461837</v>
       </c>
       <c r="O7" t="n">
-        <v>4.41661728229314</v>
+        <v>4.413671873238695</v>
       </c>
       <c r="P7" t="n">
-        <v>340.1706969228255</v>
+        <v>340.1831609626674</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21199,28 +21245,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2087640251761294</v>
+        <v>-0.2088304122455439</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1098878594390884</v>
+        <v>0.1104039413016981</v>
       </c>
       <c r="M8" t="n">
-        <v>3.776212522150729</v>
+        <v>3.767826851665609</v>
       </c>
       <c r="N8" t="n">
-        <v>20.67571403714694</v>
+        <v>20.62790931064835</v>
       </c>
       <c r="O8" t="n">
-        <v>4.547055534865056</v>
+        <v>4.541795824412228</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9090038976007</v>
+        <v>345.9096763251135</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21277,28 +21323,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1282112914676915</v>
+        <v>-0.1272885102888156</v>
       </c>
       <c r="J9" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K9" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1160734077807608</v>
+        <v>0.1149205336233038</v>
       </c>
       <c r="M9" t="n">
-        <v>2.12286884512947</v>
+        <v>2.122222078688217</v>
       </c>
       <c r="N9" t="n">
-        <v>7.331455389345745</v>
+        <v>7.325250624549944</v>
       </c>
       <c r="O9" t="n">
-        <v>2.70766604095589</v>
+        <v>2.706520021087955</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6749332549213</v>
+        <v>356.6655865032363</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21336,7 +21382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J432"/>
+  <dimension ref="A1:J433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43803,6 +43849,58 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-42.52599065035537,173.50261799490775</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-42.526647548272145,173.50250351649322</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-42.52730688356722,173.5024223567792</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-42.5279677728768,173.5023539391826</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-42.52863179956109,173.50230064723715</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-42.52929523986862,173.5022320476916</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-42.529960710163955,173.50227152351079</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-42.53061695692958,173.50249911061061</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J433"/>
+  <dimension ref="A1:J434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16032,6 +16032,42 @@
       <c r="J433" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>335.32</v>
+      </c>
+      <c r="C434" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="D434" t="n">
+        <v>332.96</v>
+      </c>
+      <c r="E434" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="F434" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="G434" t="n">
+        <v>335.04</v>
+      </c>
+      <c r="H434" t="n">
+        <v>341.38</v>
+      </c>
+      <c r="I434" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16046,7 +16082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B456"/>
+  <dimension ref="A1:B457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20609,6 +20645,16 @@
       </c>
       <c r="B456" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -20777,28 +20823,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2879963137030837</v>
+        <v>-0.2867227234255907</v>
       </c>
       <c r="J2" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K2" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1137215599505161</v>
+        <v>0.1132426894549156</v>
       </c>
       <c r="M2" t="n">
-        <v>4.854100624795321</v>
+        <v>4.849532818428248</v>
       </c>
       <c r="N2" t="n">
-        <v>37.94553524542334</v>
+        <v>37.87839857464677</v>
       </c>
       <c r="O2" t="n">
-        <v>6.159994743944457</v>
+        <v>6.154542921667439</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9459510659395</v>
+        <v>339.9330092465711</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20855,28 +20901,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3533941220194364</v>
+        <v>-0.3521053422091081</v>
       </c>
       <c r="J3" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K3" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1860989421348885</v>
+        <v>0.1855969679241443</v>
       </c>
       <c r="M3" t="n">
-        <v>4.597703609232862</v>
+        <v>4.594066784205846</v>
       </c>
       <c r="N3" t="n">
-        <v>32.06312151666916</v>
+        <v>32.01006193799702</v>
       </c>
       <c r="O3" t="n">
-        <v>5.662430707449687</v>
+        <v>5.657743537665614</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5137430894337</v>
+        <v>338.5006469188632</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20933,28 +20979,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2355659293885243</v>
+        <v>-0.2341631456846884</v>
       </c>
       <c r="J4" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1536131024601752</v>
+        <v>0.1524869457851961</v>
       </c>
       <c r="M4" t="n">
-        <v>3.394361421005534</v>
+        <v>3.395273384271744</v>
       </c>
       <c r="N4" t="n">
-        <v>17.94837252875347</v>
+        <v>17.93178812069812</v>
       </c>
       <c r="O4" t="n">
-        <v>4.236551962239278</v>
+        <v>4.234594209685046</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8929695374778</v>
+        <v>335.8787148955974</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21011,28 +21057,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0428995061898271</v>
+        <v>-0.04238259929745147</v>
       </c>
       <c r="J5" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K5" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01056309801776889</v>
+        <v>0.0103567791230974</v>
       </c>
       <c r="M5" t="n">
-        <v>2.503521247291516</v>
+        <v>2.5005225690881</v>
       </c>
       <c r="N5" t="n">
-        <v>10.11954135139022</v>
+        <v>10.09954705774222</v>
       </c>
       <c r="O5" t="n">
-        <v>3.181122655822975</v>
+        <v>3.177978454574892</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1844065765118</v>
+        <v>335.1791539330598</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21089,28 +21135,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02518460489268516</v>
+        <v>0.02502664145091174</v>
       </c>
       <c r="J6" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K6" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002949119454203508</v>
+        <v>0.002925795451216073</v>
       </c>
       <c r="M6" t="n">
-        <v>2.89602259901261</v>
+        <v>2.890104837574162</v>
       </c>
       <c r="N6" t="n">
-        <v>12.58794075365855</v>
+        <v>12.55918461703425</v>
       </c>
       <c r="O6" t="n">
-        <v>3.547948809334564</v>
+        <v>3.543893990659745</v>
       </c>
       <c r="P6" t="n">
-        <v>337.303176486961</v>
+        <v>337.3047816612202</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21167,28 +21213,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09583467928313913</v>
+        <v>-0.09694796409603464</v>
       </c>
       <c r="J7" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K7" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0269307530603401</v>
+        <v>0.02764578312609367</v>
       </c>
       <c r="M7" t="n">
-        <v>3.702686907248831</v>
+        <v>3.69983100588044</v>
       </c>
       <c r="N7" t="n">
-        <v>19.48049940461837</v>
+        <v>19.45117193579975</v>
       </c>
       <c r="O7" t="n">
-        <v>4.413671873238695</v>
+        <v>4.410348278288207</v>
       </c>
       <c r="P7" t="n">
-        <v>340.1831609626674</v>
+        <v>340.1944738088854</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21245,28 +21291,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2088304122455439</v>
+        <v>-0.2084085715876578</v>
       </c>
       <c r="J8" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K8" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104039413016981</v>
+        <v>0.1104522767769215</v>
       </c>
       <c r="M8" t="n">
-        <v>3.767826851665609</v>
+        <v>3.76142649252718</v>
       </c>
       <c r="N8" t="n">
-        <v>20.62790931064835</v>
+        <v>20.58251851693655</v>
       </c>
       <c r="O8" t="n">
-        <v>4.541795824412228</v>
+        <v>4.536796062965201</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9096763251135</v>
+        <v>345.9053897145032</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21323,28 +21369,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1272885102888156</v>
+        <v>-0.1262879727449591</v>
       </c>
       <c r="J9" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K9" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1149205336233038</v>
+        <v>0.1136182591184176</v>
       </c>
       <c r="M9" t="n">
-        <v>2.122222078688217</v>
+        <v>2.121952053454357</v>
       </c>
       <c r="N9" t="n">
-        <v>7.325250624549944</v>
+        <v>7.320983615049648</v>
       </c>
       <c r="O9" t="n">
-        <v>2.706520021087955</v>
+        <v>2.70573162287941</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6655865032363</v>
+        <v>356.6554193589099</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21382,7 +21428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J433"/>
+  <dimension ref="A1:J434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43901,6 +43947,58 @@
         </is>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-42.52599114810463,173.50262477975951</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-42.526646899413784,173.5024946718625</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-42.527306092489034,173.50241157348643</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-42.527967296693085,173.50234702899508</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-42.52863149484532,173.5022933534032</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-42.52929529822765,173.50223509064256</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-42.529960580833524,173.50228528130708</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-42.53061686906817,173.50250142102746</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J434"/>
+  <dimension ref="A1:J435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16068,6 +16068,42 @@
       <c r="J434" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="C435" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="D435" t="n">
+        <v>333.13</v>
+      </c>
+      <c r="E435" t="n">
+        <v>334.27</v>
+      </c>
+      <c r="F435" t="n">
+        <v>337.49</v>
+      </c>
+      <c r="G435" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="H435" t="n">
+        <v>342.23</v>
+      </c>
+      <c r="I435" t="n">
+        <v>355.45</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B457"/>
+  <dimension ref="A1:B458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20655,6 +20691,16 @@
       </c>
       <c r="B457" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -20823,28 +20869,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2867227234255907</v>
+        <v>-0.2856309322831355</v>
       </c>
       <c r="J2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1132426894549156</v>
+        <v>0.1129128403720784</v>
       </c>
       <c r="M2" t="n">
-        <v>4.849532818428248</v>
+        <v>4.843953807444104</v>
       </c>
       <c r="N2" t="n">
-        <v>37.87839857464677</v>
+        <v>37.80593989816179</v>
       </c>
       <c r="O2" t="n">
-        <v>6.154542921667439</v>
+        <v>6.148653502854246</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9330092465711</v>
+        <v>339.9218323708697</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20901,28 +20947,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3521053422091081</v>
+        <v>-0.35118949093975</v>
       </c>
       <c r="J3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1855969679241443</v>
+        <v>0.1854757674126825</v>
       </c>
       <c r="M3" t="n">
-        <v>4.594066784205846</v>
+        <v>4.588364900568608</v>
       </c>
       <c r="N3" t="n">
-        <v>32.01006193799702</v>
+        <v>31.94673357903813</v>
       </c>
       <c r="O3" t="n">
-        <v>5.657743537665614</v>
+        <v>5.652144157666021</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5006469188632</v>
+        <v>338.4912711734477</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20979,28 +21025,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2341631456846884</v>
+        <v>-0.2326724955204413</v>
       </c>
       <c r="J4" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K4" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1524869457851961</v>
+        <v>0.1512527438357977</v>
       </c>
       <c r="M4" t="n">
-        <v>3.395273384271744</v>
+        <v>3.396655446630089</v>
       </c>
       <c r="N4" t="n">
-        <v>17.93178812069812</v>
+        <v>17.91809444777089</v>
       </c>
       <c r="O4" t="n">
-        <v>4.234594209685046</v>
+        <v>4.232977019518402</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8787148955974</v>
+        <v>335.8634548234535</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21057,28 +21103,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04238259929745147</v>
+        <v>-0.04229087859771778</v>
       </c>
       <c r="J5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0103567791230974</v>
+        <v>0.01036077750858799</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5005225690881</v>
+        <v>2.495248666976697</v>
       </c>
       <c r="N5" t="n">
-        <v>10.09954705774222</v>
+        <v>10.07638079637315</v>
       </c>
       <c r="O5" t="n">
-        <v>3.177978454574892</v>
+        <v>3.174331551110114</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1791539330598</v>
+        <v>335.1782149706335</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21135,28 +21181,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02502664145091174</v>
+        <v>0.0248184719395864</v>
       </c>
       <c r="J6" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K6" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002925795451216073</v>
+        <v>0.002890953160994636</v>
       </c>
       <c r="M6" t="n">
-        <v>2.890104837574162</v>
+        <v>2.884442885954367</v>
       </c>
       <c r="N6" t="n">
-        <v>12.55918461703425</v>
+        <v>12.5307851276987</v>
       </c>
       <c r="O6" t="n">
-        <v>3.543893990659745</v>
+        <v>3.539884903171105</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3047816612202</v>
+        <v>337.3069127325053</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21213,28 +21259,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09694796409603464</v>
+        <v>-0.09789761661409874</v>
       </c>
       <c r="J7" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K7" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02764578312609367</v>
+        <v>0.02828872132535087</v>
       </c>
       <c r="M7" t="n">
-        <v>3.69983100588044</v>
+        <v>3.696082698040653</v>
       </c>
       <c r="N7" t="n">
-        <v>19.45117193579975</v>
+        <v>19.41756501203639</v>
       </c>
       <c r="O7" t="n">
-        <v>4.410348278288207</v>
+        <v>4.406536623249193</v>
       </c>
       <c r="P7" t="n">
-        <v>340.1944738088854</v>
+        <v>340.2041955841784</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21291,28 +21337,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2084085715876578</v>
+        <v>-0.2076071100672414</v>
       </c>
       <c r="J8" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K8" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104522767769215</v>
+        <v>0.1101224283894863</v>
       </c>
       <c r="M8" t="n">
-        <v>3.76142649252718</v>
+        <v>3.757060214853502</v>
       </c>
       <c r="N8" t="n">
-        <v>20.58251851693655</v>
+        <v>20.54307877394445</v>
       </c>
       <c r="O8" t="n">
-        <v>4.536796062965201</v>
+        <v>4.532447327211255</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9053897145032</v>
+        <v>345.8971849989264</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21369,28 +21415,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1262879727449591</v>
+        <v>-0.1253632230267275</v>
       </c>
       <c r="J9" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K9" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1136182591184176</v>
+        <v>0.1124732156477033</v>
       </c>
       <c r="M9" t="n">
-        <v>2.121952053454357</v>
+        <v>2.121357761388408</v>
       </c>
       <c r="N9" t="n">
-        <v>7.320983615049648</v>
+        <v>7.31474614660934</v>
       </c>
       <c r="O9" t="n">
-        <v>2.70573162287941</v>
+        <v>2.704578737365459</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6554193589099</v>
+        <v>356.6459525183636</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21428,7 +21474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J434"/>
+  <dimension ref="A1:J435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43999,6 +44045,58 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-42.525990730350806,173.50261908533034</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-42.526646072785006,173.5024834040456</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-42.527306243593934,173.50241363321646</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-42.52796646963617,173.50233502709062</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-42.52863143898071,173.50229201620033</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-42.52929538226452,173.502239472492</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-42.529960483548486,173.50229563009185</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-42.530616961553854,173.50249898900975</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J435"/>
+  <dimension ref="A1:J437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16102,6 +16102,78 @@
         <v>355.45</v>
       </c>
       <c r="J435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="C436" t="n">
+        <v>330.61</v>
+      </c>
+      <c r="D436" t="n">
+        <v>332.68</v>
+      </c>
+      <c r="E436" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="F436" t="n">
+        <v>337.48</v>
+      </c>
+      <c r="G436" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="H436" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="I436" t="n">
+        <v>355.39</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>330.83</v>
+      </c>
+      <c r="C437" t="n">
+        <v>328.36</v>
+      </c>
+      <c r="D437" t="n">
+        <v>331.05</v>
+      </c>
+      <c r="E437" t="n">
+        <v>332.48</v>
+      </c>
+      <c r="F437" t="n">
+        <v>337.8</v>
+      </c>
+      <c r="G437" t="n">
+        <v>336.22</v>
+      </c>
+      <c r="H437" t="n">
+        <v>342.69</v>
+      </c>
+      <c r="I437" t="n">
+        <v>354.91</v>
+      </c>
+      <c r="J437" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16118,7 +16190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:B460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20701,6 +20773,26 @@
       </c>
       <c r="B458" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -20869,28 +20961,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2856309322831355</v>
+        <v>-0.2855927219156284</v>
       </c>
       <c r="J2" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K2" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1129128403720784</v>
+        <v>0.1138071901690356</v>
       </c>
       <c r="M2" t="n">
-        <v>4.843953807444104</v>
+        <v>4.828691512203487</v>
       </c>
       <c r="N2" t="n">
-        <v>37.80593989816179</v>
+        <v>37.64310843604446</v>
       </c>
       <c r="O2" t="n">
-        <v>6.148653502854246</v>
+        <v>6.135397985138736</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9218323708697</v>
+        <v>339.9214538586348</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20947,28 +21039,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.35118949093975</v>
+        <v>-0.3508894946612799</v>
       </c>
       <c r="J3" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K3" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1854757674126825</v>
+        <v>0.1866173643270189</v>
       </c>
       <c r="M3" t="n">
-        <v>4.588364900568608</v>
+        <v>4.572450431586607</v>
       </c>
       <c r="N3" t="n">
-        <v>31.94673357903813</v>
+        <v>31.80652797430329</v>
       </c>
       <c r="O3" t="n">
-        <v>5.652144157666021</v>
+        <v>5.63972765072067</v>
       </c>
       <c r="P3" t="n">
-        <v>338.4912711734477</v>
+        <v>338.4882007172579</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21025,28 +21117,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2326724955204413</v>
+        <v>-0.2308015523001694</v>
       </c>
       <c r="J4" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1512527438357977</v>
+        <v>0.1502164259449162</v>
       </c>
       <c r="M4" t="n">
-        <v>3.396655446630089</v>
+        <v>3.392521369890283</v>
       </c>
       <c r="N4" t="n">
-        <v>17.91809444777089</v>
+        <v>17.86080564686665</v>
       </c>
       <c r="O4" t="n">
-        <v>4.232977019518402</v>
+        <v>4.226204638545873</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8634548234535</v>
+        <v>335.8442492573941</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21103,28 +21195,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04229087859771778</v>
+        <v>-0.04307507451610565</v>
       </c>
       <c r="J5" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01036077750858799</v>
+        <v>0.01083910471757299</v>
       </c>
       <c r="M5" t="n">
-        <v>2.495248666976697</v>
+        <v>2.488028649922648</v>
       </c>
       <c r="N5" t="n">
-        <v>10.07638079637315</v>
+        <v>10.035945360745</v>
       </c>
       <c r="O5" t="n">
-        <v>3.174331551110114</v>
+        <v>3.167956022539612</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1782149706335</v>
+        <v>335.1862739541731</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21181,28 +21273,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0248184719395864</v>
+        <v>0.02454045762221235</v>
       </c>
       <c r="J6" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K6" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002890953160994636</v>
+        <v>0.002853347666729955</v>
       </c>
       <c r="M6" t="n">
-        <v>2.884442885954367</v>
+        <v>2.872529830148006</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5307851276987</v>
+        <v>12.47390248250562</v>
       </c>
       <c r="O6" t="n">
-        <v>3.539884903171105</v>
+        <v>3.531841231214339</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3069127325053</v>
+        <v>337.3097662564696</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21259,28 +21351,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09789761661409874</v>
+        <v>-0.0992820185951433</v>
       </c>
       <c r="J7" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K7" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02828872132535087</v>
+        <v>0.02932080403878823</v>
       </c>
       <c r="M7" t="n">
-        <v>3.696082698040653</v>
+        <v>3.686018711176291</v>
       </c>
       <c r="N7" t="n">
-        <v>19.41756501203639</v>
+        <v>19.34076865043476</v>
       </c>
       <c r="O7" t="n">
-        <v>4.406536623249193</v>
+        <v>4.397814076383261</v>
       </c>
       <c r="P7" t="n">
-        <v>340.2041955841784</v>
+        <v>340.218409861602</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21337,28 +21429,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2076071100672414</v>
+        <v>-0.2058135887149</v>
       </c>
       <c r="J8" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K8" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1101224283894863</v>
+        <v>0.1092534050109442</v>
       </c>
       <c r="M8" t="n">
-        <v>3.757060214853502</v>
+        <v>3.749345614182065</v>
       </c>
       <c r="N8" t="n">
-        <v>20.54307877394445</v>
+        <v>20.46915746657051</v>
       </c>
       <c r="O8" t="n">
-        <v>4.532447327211255</v>
+        <v>4.524285298980438</v>
       </c>
       <c r="P8" t="n">
-        <v>345.8971849989264</v>
+        <v>345.878765011645</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21415,28 +21507,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1253632230267275</v>
+        <v>-0.1237913795842352</v>
       </c>
       <c r="J9" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K9" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1124732156477033</v>
+        <v>0.1106947134446151</v>
       </c>
       <c r="M9" t="n">
-        <v>2.121357761388408</v>
+        <v>2.118860800824039</v>
       </c>
       <c r="N9" t="n">
-        <v>7.31474614660934</v>
+        <v>7.29688473524943</v>
       </c>
       <c r="O9" t="n">
-        <v>2.704578737365459</v>
+        <v>2.70127465009566</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6459525183636</v>
+        <v>356.6298132047871</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21474,7 +21566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J435"/>
+  <dimension ref="A1:J437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44097,6 +44189,110 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-42.52598986817711,173.50260733299805</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-42.52664548614457,173.50247540753054</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-42.52730584361029,173.50240818098987</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-42.52796606028431,173.50232908675423</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-42.52863143390213,173.50229189463641</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-42.529295454629484,173.50224324575123</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-42.529960481259415,173.5022958735927</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-42.53061698929955,173.5024982594044</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-42.525987157210736,173.50257037979026</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-42.52664348622976,173.50244814668483</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-42.527304394778476,173.5023884318141</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-42.52796497424724,173.50231332667838</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-42.52863159641729,173.50229578468117</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-42.52929557368124,173.5022494533713</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-42.52996043089971,173.50230123061067</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-42.53061721126495,173.50249242256186</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J437"/>
+  <dimension ref="A1:J440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16174,6 +16174,114 @@
         <v>354.91</v>
       </c>
       <c r="J437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>329.53</v>
+      </c>
+      <c r="C438" t="n">
+        <v>326.48</v>
+      </c>
+      <c r="D438" t="n">
+        <v>329.1</v>
+      </c>
+      <c r="E438" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="F438" t="n">
+        <v>337</v>
+      </c>
+      <c r="G438" t="n">
+        <v>335.37</v>
+      </c>
+      <c r="H438" t="n">
+        <v>341.59</v>
+      </c>
+      <c r="I438" t="n">
+        <v>352.58</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>328.23</v>
+      </c>
+      <c r="C439" t="n">
+        <v>325.03</v>
+      </c>
+      <c r="D439" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="E439" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="F439" t="n">
+        <v>337.07</v>
+      </c>
+      <c r="G439" t="n">
+        <v>335.67</v>
+      </c>
+      <c r="H439" t="n">
+        <v>341.46</v>
+      </c>
+      <c r="I439" t="n">
+        <v>352.65</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>327.19</v>
+      </c>
+      <c r="C440" t="n">
+        <v>324.78</v>
+      </c>
+      <c r="D440" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="E440" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="F440" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="G440" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="H440" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="I440" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="J440" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16190,7 +16298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B460"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20793,6 +20901,36 @@
       </c>
       <c r="B460" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -20961,28 +21099,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2855927219156284</v>
+        <v>-0.2905929694260139</v>
       </c>
       <c r="J2" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1138071901690356</v>
+        <v>0.1185090257690545</v>
       </c>
       <c r="M2" t="n">
-        <v>4.828691512203487</v>
+        <v>4.823471613243254</v>
       </c>
       <c r="N2" t="n">
-        <v>37.64310843604446</v>
+        <v>37.49734473226471</v>
       </c>
       <c r="O2" t="n">
-        <v>6.135397985138736</v>
+        <v>6.123507551417301</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9214538586348</v>
+        <v>339.9730256418155</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21039,28 +21177,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3508894946612799</v>
+        <v>-0.3555168122574645</v>
       </c>
       <c r="J3" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K3" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1866173643270189</v>
+        <v>0.1923454378737824</v>
       </c>
       <c r="M3" t="n">
-        <v>4.572450431586607</v>
+        <v>4.565931722996145</v>
       </c>
       <c r="N3" t="n">
-        <v>31.80652797430329</v>
+        <v>31.68311800423376</v>
       </c>
       <c r="O3" t="n">
-        <v>5.63972765072067</v>
+        <v>5.628775888613239</v>
       </c>
       <c r="P3" t="n">
-        <v>338.4882007172579</v>
+        <v>338.5359240184171</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21117,28 +21255,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2308015523001694</v>
+        <v>-0.2319407294300223</v>
       </c>
       <c r="J4" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K4" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1502164259449162</v>
+        <v>0.1532473157364037</v>
       </c>
       <c r="M4" t="n">
-        <v>3.392521369890283</v>
+        <v>3.374565279315669</v>
       </c>
       <c r="N4" t="n">
-        <v>17.86080564686665</v>
+        <v>17.74522911655367</v>
       </c>
       <c r="O4" t="n">
-        <v>4.226204638545873</v>
+        <v>4.212508648840222</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8442492573941</v>
+        <v>335.8560001000135</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21195,28 +21333,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04307507451610565</v>
+        <v>-0.04476354915571068</v>
       </c>
       <c r="J5" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K5" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01083910471757299</v>
+        <v>0.01184490857065834</v>
       </c>
       <c r="M5" t="n">
-        <v>2.488028649922648</v>
+        <v>2.480079238607756</v>
       </c>
       <c r="N5" t="n">
-        <v>10.035945360745</v>
+        <v>9.979442814028184</v>
       </c>
       <c r="O5" t="n">
-        <v>3.167956022539612</v>
+        <v>3.159025611486584</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1862739541731</v>
+        <v>335.2036841258339</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21273,28 +21411,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02454045762221235</v>
+        <v>0.02338714862897012</v>
       </c>
       <c r="J6" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K6" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002853347666729955</v>
+        <v>0.002627572646641485</v>
       </c>
       <c r="M6" t="n">
-        <v>2.872529830148006</v>
+        <v>2.858276955980497</v>
       </c>
       <c r="N6" t="n">
-        <v>12.47390248250562</v>
+        <v>12.39427263359575</v>
       </c>
       <c r="O6" t="n">
-        <v>3.531841231214339</v>
+        <v>3.520550047023299</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3097662564696</v>
+        <v>337.3216585371466</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21351,28 +21489,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0992820185951433</v>
+        <v>-0.1014033440759645</v>
       </c>
       <c r="J7" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K7" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02932080403878823</v>
+        <v>0.03093530888773599</v>
       </c>
       <c r="M7" t="n">
-        <v>3.686018711176291</v>
+        <v>3.671232400435026</v>
       </c>
       <c r="N7" t="n">
-        <v>19.34076865043476</v>
+        <v>19.22944437961498</v>
       </c>
       <c r="O7" t="n">
-        <v>4.397814076383261</v>
+        <v>4.385139037660606</v>
       </c>
       <c r="P7" t="n">
-        <v>340.218409861602</v>
+        <v>340.2402788542125</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21429,28 +21567,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2058135887149</v>
+        <v>-0.2046481550183807</v>
       </c>
       <c r="J8" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K8" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1092534050109442</v>
+        <v>0.1094865562479198</v>
       </c>
       <c r="M8" t="n">
-        <v>3.749345614182065</v>
+        <v>3.729850691900816</v>
       </c>
       <c r="N8" t="n">
-        <v>20.46915746657051</v>
+        <v>20.33570436874924</v>
       </c>
       <c r="O8" t="n">
-        <v>4.524285298980438</v>
+        <v>4.509512653131073</v>
       </c>
       <c r="P8" t="n">
-        <v>345.878765011645</v>
+        <v>345.8667506740044</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21507,28 +21645,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1237913795842352</v>
+        <v>-0.124556728510765</v>
       </c>
       <c r="J9" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K9" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1106947134446151</v>
+        <v>0.1132836599690467</v>
       </c>
       <c r="M9" t="n">
-        <v>2.118860800824039</v>
+        <v>2.109038408464061</v>
       </c>
       <c r="N9" t="n">
-        <v>7.29688473524943</v>
+        <v>7.249627522640392</v>
       </c>
       <c r="O9" t="n">
-        <v>2.70127465009566</v>
+        <v>2.692513235369585</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6298132047871</v>
+        <v>356.6377037836082</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21566,7 +21704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J437"/>
+  <dimension ref="A1:J440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44293,6 +44431,162 @@
         </is>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-42.52598600171325,173.5025546292436</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-42.526641815184846,173.50242536873503</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-42.527302661508934,173.50236480550063</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-42.52796504108034,173.5023142965292</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-42.52863119012909,173.5022860595693</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-42.52929537526146,173.50223910733786</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-42.529960556798486,173.50228783806568</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-42.53061828871776,173.50246408955468</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-42.525984846213596,173.50253887869752</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-42.52664052634393,173.50240780063623</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-42.52730255484603,173.5023633515737</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-42.5279652081631,173.5023167211562</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-42.528631225679334,173.5022869105166</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-42.529295445292085,173.50224275887905</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-42.52996057167733,173.50228625531037</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-42.53061825634804,173.5024649407609</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-42.52598392181231,173.50252627826103</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-42.526640304129714,173.50240477165377</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-42.527301879313896,173.50235414336984</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-42.5279652081631,173.5023167211562</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-42.52863123075796,173.5022870320805</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-42.52929566005191,173.50225395693877</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-42.52996064149314,173.5022788285354</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-42.53061813611757,173.50246810238409</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J440"/>
+  <dimension ref="A1:J442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16282,6 +16282,78 @@
         <v>352.91</v>
       </c>
       <c r="J440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>326.27</v>
+      </c>
+      <c r="C441" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="D441" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="E441" t="n">
+        <v>331.83</v>
+      </c>
+      <c r="F441" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="G441" t="n">
+        <v>336.21</v>
+      </c>
+      <c r="H441" t="n">
+        <v>339.79</v>
+      </c>
+      <c r="I441" t="n">
+        <v>352.35</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>324.04</v>
+      </c>
+      <c r="C442" t="n">
+        <v>322.96</v>
+      </c>
+      <c r="D442" t="n">
+        <v>324.98</v>
+      </c>
+      <c r="E442" t="n">
+        <v>330.76</v>
+      </c>
+      <c r="F442" t="n">
+        <v>336.03</v>
+      </c>
+      <c r="G442" t="n">
+        <v>336.36</v>
+      </c>
+      <c r="H442" t="n">
+        <v>339.13</v>
+      </c>
+      <c r="I442" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="J442" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16298,7 +16370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B463"/>
+  <dimension ref="A1:B465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20931,6 +21003,26 @@
       </c>
       <c r="B463" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -21099,28 +21191,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2905929694260139</v>
+        <v>-0.2964481080934996</v>
       </c>
       <c r="J2" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1185090257690545</v>
+        <v>0.1230857686898565</v>
       </c>
       <c r="M2" t="n">
-        <v>4.823471613243254</v>
+        <v>4.833834806378709</v>
       </c>
       <c r="N2" t="n">
-        <v>37.49734473226471</v>
+        <v>37.55399049005479</v>
       </c>
       <c r="O2" t="n">
-        <v>6.123507551417301</v>
+        <v>6.12813107644205</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9730256418155</v>
+        <v>340.0335644604685</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21177,28 +21269,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3555168122574645</v>
+        <v>-0.3598595371817798</v>
       </c>
       <c r="J3" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1923454378737824</v>
+        <v>0.1969843643365203</v>
       </c>
       <c r="M3" t="n">
-        <v>4.565931722996145</v>
+        <v>4.568289338419998</v>
       </c>
       <c r="N3" t="n">
-        <v>31.68311800423376</v>
+        <v>31.6641424184687</v>
       </c>
       <c r="O3" t="n">
-        <v>5.628775888613239</v>
+        <v>5.627090048903492</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5359240184171</v>
+        <v>338.5808253358472</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21255,28 +21347,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2319407294300223</v>
+        <v>-0.2349214765174643</v>
       </c>
       <c r="J4" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1532473157364037</v>
+        <v>0.1573474738399157</v>
       </c>
       <c r="M4" t="n">
-        <v>3.374565279315669</v>
+        <v>3.372813624891959</v>
       </c>
       <c r="N4" t="n">
-        <v>17.74522911655367</v>
+        <v>17.72734291220203</v>
       </c>
       <c r="O4" t="n">
-        <v>4.212508648840222</v>
+        <v>4.210385126351511</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8560001000135</v>
+        <v>335.8868216604814</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21333,28 +21425,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04476354915571068</v>
+        <v>-0.04701951931545586</v>
       </c>
       <c r="J5" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K5" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01184490857065834</v>
+        <v>0.01312819069392146</v>
       </c>
       <c r="M5" t="n">
-        <v>2.480079238607756</v>
+        <v>2.480809516309856</v>
       </c>
       <c r="N5" t="n">
-        <v>9.979442814028184</v>
+        <v>9.968313468682785</v>
       </c>
       <c r="O5" t="n">
-        <v>3.159025611486584</v>
+        <v>3.157263604560567</v>
       </c>
       <c r="P5" t="n">
-        <v>335.2036841258339</v>
+        <v>335.2270100700038</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21411,28 +21503,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02338714862897012</v>
+        <v>0.02193024491647036</v>
       </c>
       <c r="J6" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K6" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002627572646641485</v>
+        <v>0.002329968237157365</v>
       </c>
       <c r="M6" t="n">
-        <v>2.858276955980497</v>
+        <v>2.85203623577257</v>
       </c>
       <c r="N6" t="n">
-        <v>12.39427263359575</v>
+        <v>12.35188785518296</v>
       </c>
       <c r="O6" t="n">
-        <v>3.520550047023299</v>
+        <v>3.514525267398565</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3216585371466</v>
+        <v>337.3367216275735</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21489,28 +21581,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1014033440759645</v>
+        <v>-0.1024315845094582</v>
       </c>
       <c r="J7" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K7" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03093530888773599</v>
+        <v>0.03181895088598974</v>
       </c>
       <c r="M7" t="n">
-        <v>3.671232400435026</v>
+        <v>3.659594156101076</v>
       </c>
       <c r="N7" t="n">
-        <v>19.22944437961498</v>
+        <v>19.14908173657968</v>
       </c>
       <c r="O7" t="n">
-        <v>4.385139037660606</v>
+        <v>4.375966377450777</v>
       </c>
       <c r="P7" t="n">
-        <v>340.2402788542125</v>
+        <v>340.2509090614092</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21567,28 +21659,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2046481550183807</v>
+        <v>-0.2054145949102705</v>
       </c>
       <c r="J8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1094865562479198</v>
+        <v>0.1111077247066289</v>
       </c>
       <c r="M8" t="n">
-        <v>3.729850691900816</v>
+        <v>3.71716955142503</v>
       </c>
       <c r="N8" t="n">
-        <v>20.33570436874924</v>
+        <v>20.24775712053998</v>
       </c>
       <c r="O8" t="n">
-        <v>4.509512653131073</v>
+        <v>4.499750784270166</v>
       </c>
       <c r="P8" t="n">
-        <v>345.8667506740044</v>
+        <v>345.8746760555709</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21645,28 +21737,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.124556728510765</v>
+        <v>-0.1256619150960107</v>
       </c>
       <c r="J9" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K9" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1132836599690467</v>
+        <v>0.1158956724578729</v>
       </c>
       <c r="M9" t="n">
-        <v>2.109038408464061</v>
+        <v>2.106150820949436</v>
       </c>
       <c r="N9" t="n">
-        <v>7.249627522640392</v>
+        <v>7.225253594365268</v>
       </c>
       <c r="O9" t="n">
-        <v>2.692513235369585</v>
+        <v>2.687983183423079</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6377037836082</v>
+        <v>356.6491315190722</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21704,7 +21796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J440"/>
+  <dimension ref="A1:J442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44587,6 +44679,110 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-42.52598310407154,173.5025151317214</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-42.52664016191256,173.50240283310498</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-42.52730092823451,173.50234117918845</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-42.527964431227886,173.50230544664066</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-42.52863087017655,173.50227840104378</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-42.529295571346886,173.50224933165325</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-42.52996076281127,173.50226592299194</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-42.53061839507539,173.50246129273413</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-42.525981121934535,173.5024881134797</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-42.52663868640773,173.50238272066193</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-42.52729899940546,173.5023148873451</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-42.52796353733332,173.50229247488653</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-42.52863069750352,173.50227426787134</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-42.529295606362055,173.50225115742384</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-42.52996083834825,173.50225788746482</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-42.53061874189325,173.5024521726672</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J442"/>
+  <dimension ref="A1:J443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16354,6 +16354,42 @@
         <v>351.6</v>
       </c>
       <c r="J442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>325.31</v>
+      </c>
+      <c r="C443" t="n">
+        <v>323.24</v>
+      </c>
+      <c r="D443" t="n">
+        <v>326.16</v>
+      </c>
+      <c r="E443" t="n">
+        <v>330.75</v>
+      </c>
+      <c r="F443" t="n">
+        <v>334.55</v>
+      </c>
+      <c r="G443" t="n">
+        <v>335.54</v>
+      </c>
+      <c r="H443" t="n">
+        <v>338.92</v>
+      </c>
+      <c r="I443" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="J443" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16370,7 +16406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B465"/>
+  <dimension ref="A1:B466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21023,6 +21059,16 @@
       </c>
       <c r="B465" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -21191,28 +21237,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2964481080934996</v>
+        <v>-0.2992646366082286</v>
       </c>
       <c r="J2" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1230857686898565</v>
+        <v>0.1253517106326697</v>
       </c>
       <c r="M2" t="n">
-        <v>4.833834806378709</v>
+        <v>4.838313145771789</v>
       </c>
       <c r="N2" t="n">
-        <v>37.55399049005479</v>
+        <v>37.57143278641804</v>
       </c>
       <c r="O2" t="n">
-        <v>6.12813107644205</v>
+        <v>6.129554044660838</v>
       </c>
       <c r="P2" t="n">
-        <v>340.0335644604685</v>
+        <v>340.0628194122859</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21269,28 +21315,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3598595371817798</v>
+        <v>-0.3622224518901088</v>
       </c>
       <c r="J3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1969843643365203</v>
+        <v>0.1994408765212791</v>
       </c>
       <c r="M3" t="n">
-        <v>4.568289338419998</v>
+        <v>4.570383300703447</v>
       </c>
       <c r="N3" t="n">
-        <v>31.6641424184687</v>
+        <v>31.66458055752791</v>
       </c>
       <c r="O3" t="n">
-        <v>5.627090048903492</v>
+        <v>5.627128979997519</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5808253358472</v>
+        <v>338.6053686541836</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21347,28 +21393,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2349214765174643</v>
+        <v>-0.2363437875446329</v>
       </c>
       <c r="J4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1573474738399157</v>
+        <v>0.159379176342599</v>
       </c>
       <c r="M4" t="n">
-        <v>3.372813624891959</v>
+        <v>3.371632747296073</v>
       </c>
       <c r="N4" t="n">
-        <v>17.72734291220203</v>
+        <v>17.71335059368641</v>
       </c>
       <c r="O4" t="n">
-        <v>4.210385126351511</v>
+        <v>4.208723154792485</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8868216604814</v>
+        <v>335.901595038543</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21425,28 +21471,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04701951931545586</v>
+        <v>-0.04835885891767457</v>
       </c>
       <c r="J5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01312819069392146</v>
+        <v>0.01390801924975682</v>
       </c>
       <c r="M5" t="n">
-        <v>2.480809516309856</v>
+        <v>2.482286698337871</v>
       </c>
       <c r="N5" t="n">
-        <v>9.968313468682785</v>
+        <v>9.968917539028594</v>
       </c>
       <c r="O5" t="n">
-        <v>3.157263604560567</v>
+        <v>3.157359266701937</v>
       </c>
       <c r="P5" t="n">
-        <v>335.2270100700038</v>
+        <v>335.2409216335918</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21503,28 +21549,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02193024491647036</v>
+        <v>0.02051946940904694</v>
       </c>
       <c r="J6" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K6" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002329968237157365</v>
+        <v>0.002045655810144709</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85203623577257</v>
+        <v>2.852011615958245</v>
       </c>
       <c r="N6" t="n">
-        <v>12.35188785518296</v>
+        <v>12.34963531436038</v>
       </c>
       <c r="O6" t="n">
-        <v>3.514525267398565</v>
+        <v>3.514204791181126</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3367216275735</v>
+        <v>337.3513751875424</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21581,28 +21627,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1024315845094582</v>
+        <v>-0.1032471356408707</v>
       </c>
       <c r="J7" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K7" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03181895088598974</v>
+        <v>0.03244270690256168</v>
       </c>
       <c r="M7" t="n">
-        <v>3.659594156101076</v>
+        <v>3.655242243483534</v>
       </c>
       <c r="N7" t="n">
-        <v>19.14908173657968</v>
+        <v>19.1143441986771</v>
       </c>
       <c r="O7" t="n">
-        <v>4.375966377450777</v>
+        <v>4.371995448153748</v>
       </c>
       <c r="P7" t="n">
-        <v>340.2509090614092</v>
+        <v>340.2593800954958</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21659,28 +21705,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2054145949102705</v>
+        <v>-0.2060110640720947</v>
       </c>
       <c r="J8" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K8" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1111077247066289</v>
+        <v>0.1121209352943822</v>
       </c>
       <c r="M8" t="n">
-        <v>3.71716955142503</v>
+        <v>3.712042398236513</v>
       </c>
       <c r="N8" t="n">
-        <v>20.24775712053998</v>
+        <v>20.2065404716719</v>
       </c>
       <c r="O8" t="n">
-        <v>4.499750784270166</v>
+        <v>4.495168569883881</v>
       </c>
       <c r="P8" t="n">
-        <v>345.8746760555709</v>
+        <v>345.8808715108977</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21737,28 +21783,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1256619150960107</v>
+        <v>-0.1265389626691696</v>
       </c>
       <c r="J9" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K9" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1158956724578729</v>
+        <v>0.1176677008777737</v>
       </c>
       <c r="M9" t="n">
-        <v>2.106150820949436</v>
+        <v>2.106641558643504</v>
       </c>
       <c r="N9" t="n">
-        <v>7.225253594365268</v>
+        <v>7.218836740406545</v>
       </c>
       <c r="O9" t="n">
-        <v>2.687983183423079</v>
+        <v>2.686789299592833</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6491315190722</v>
+        <v>356.6582413094969</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21796,7 +21842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J442"/>
+  <dimension ref="A1:J443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44783,6 +44829,58 @@
         </is>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-42.52598225077567,173.5025035005499</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-42.526638935288325,173.50238611312216</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-42.52730004826255,173.502329184292</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-42.52796352897916,173.50229235365518</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-42.5286299458663,173.50225627641495</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-42.52929541494549,173.50224117654454</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-42.52996086238262,173.5022553307062</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-42.53061894073517,173.50244694382877</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
